--- a/Pitta_rawdata.xlsx
+++ b/Pitta_rawdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agoujun/Desktop/Pitta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8548687-C4F7-5F45-ADDD-F687CC5F6393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AACE886-F2C3-0D45-A484-3E848E299B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27940" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
